--- a/data/trans_orig/barthel_r-Edad-trans_orig.xlsx
+++ b/data/trans_orig/barthel_r-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>266543</t>
+          <t>265851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>282459</t>
+          <t>282456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>294410</t>
+          <t>296031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>317899</t>
+          <t>317404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>566745</t>
+          <t>566750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>595041</t>
+          <t>595458</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>18611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28668</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12366</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26051</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16908</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147709</t>
+          <t>147261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>170609</t>
+          <t>171402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>213671</t>
+          <t>213862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248627</t>
+          <t>248403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>370408</t>
+          <t>366699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413202</t>
+          <t>411477</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29387</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48775</t>
+          <t>47908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42814</t>
+          <t>42720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70810</t>
+          <t>70856</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,03%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>32304</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58376</t>
+          <t>57991</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>51607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81793</t>
+          <t>82206</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>11880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>419306</t>
+          <t>418670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>448807</t>
+          <t>447671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>515934</t>
+          <t>514436</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>558877</t>
+          <t>558410</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>948060</t>
+          <t>948531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1000478</t>
+          <t>1000839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>61542</t>
+          <t>61466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>89687</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40544</t>
+          <t>41248</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>76922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70831</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>108646</t>
+          <t>108104</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>50319</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>267467</t>
+          <t>266187</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>288447</t>
+          <t>288685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>279873</t>
+          <t>279018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308267</t>
+          <t>308964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>556213</t>
+          <t>555688</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>591909</t>
+          <t>592736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26424</t>
+          <t>26330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15160</t>
+          <t>14768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33284</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23853</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45921</t>
+          <t>47690</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>155548</t>
+          <t>159073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189500</t>
+          <t>190355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191586</t>
+          <t>191292</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>230967</t>
+          <t>232855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>361520</t>
+          <t>360519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413410</t>
+          <t>416558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8443</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>26634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15935</t>
+          <t>16451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37121</t>
+          <t>37162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57796</t>
+          <t>55730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53350</t>
+          <t>54514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84121</t>
+          <t>82883</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118067</t>
+          <t>119140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117065</t>
+          <t>118460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160366</t>
+          <t>162499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>9608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28653</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>50057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41788</t>
+          <t>41090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72161</t>
+          <t>70857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23276</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>432743</t>
+          <t>433418</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>473497</t>
+          <t>473366</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>482401</t>
+          <t>483610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>535634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>931368</t>
+          <t>929441</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>996504</t>
+          <t>991230</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,1%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55252</t>
+          <t>55770</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81381</t>
+          <t>81685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72738</t>
+          <t>73249</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>115387</t>
+          <t>115155</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157887</t>
+          <t>159663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>163434</t>
+          <t>165694</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>217574</t>
+          <t>216403</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31199</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58573</t>
+          <t>58446</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49309</t>
+          <t>49381</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83470</t>
+          <t>81674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25176</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13845</t>
+          <t>13867</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32420</t>
+          <t>32993</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>295317</t>
+          <t>294613</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>316566</t>
+          <t>315879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>290093</t>
+          <t>294597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>323255</t>
+          <t>324681</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>597232</t>
+          <t>595116</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>633637</t>
+          <t>633700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24164</t>
+          <t>23738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46845</t>
+          <t>46247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30915</t>
+          <t>30157</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56468</t>
+          <t>56951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25188</t>
+          <t>24815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45864</t>
+          <t>42959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34287</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>60161</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12157</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169553</t>
+          <t>170258</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>196186</t>
+          <t>196635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>202688</t>
+          <t>206003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249777</t>
+          <t>250339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>383622</t>
+          <t>381322</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>439912</t>
+          <t>436434</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15833</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31859</t>
+          <t>32369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24869</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51288</t>
+          <t>51424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44723</t>
+          <t>46720</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76872</t>
+          <t>79578</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,11%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43044</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78707</t>
+          <t>78514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118012</t>
+          <t>117865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107678</t>
+          <t>108533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150429</t>
+          <t>153312</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20285</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42422</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34945</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63122</t>
+          <t>61032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19499</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>471946</t>
+          <t>472970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>507409</t>
+          <t>506860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507130</t>
+          <t>508571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>562905</t>
+          <t>563315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>992970</t>
+          <t>995354</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1059815</t>
+          <t>1060253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>21484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41954</t>
+          <t>42537</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55552</t>
+          <t>54878</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90654</t>
+          <t>90706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83549</t>
+          <t>82450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124715</t>
+          <t>123771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35038</t>
+          <t>35216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61410</t>
+          <t>61378</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107238</t>
+          <t>106620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>154483</t>
+          <t>152778</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>149103</t>
+          <t>150172</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>200783</t>
+          <t>204051</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46110</t>
+          <t>44994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39528</t>
+          <t>39632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67937</t>
+          <t>68545</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>7825</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -7556,32 +7556,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>320592</t>
+          <t>355280</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>310279</t>
+          <t>345284</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>331092</t>
+          <t>366040</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7591,32 +7591,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>533138</t>
+          <t>355472</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>492279</t>
+          <t>343109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>573325</t>
+          <t>366555</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7626,32 +7626,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>853729</t>
+          <t>710751</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>815738</t>
+          <t>693432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>913095</t>
+          <t>726927</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -7669,32 +7669,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23512</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31411</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7704,32 +7704,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41253</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>36018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65468</t>
+          <t>55237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7739,32 +7739,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>64765</t>
+          <t>71596</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85441</t>
+          <t>85107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -7782,32 +7782,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26768</t>
+          <t>29571</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7852,32 +7852,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>44256</t>
+          <t>49263</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>39115</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61341</t>
+          <t>60596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -7895,32 +7895,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7965,32 +7965,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>7096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -8053,12 +8053,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -8121,17 +8121,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8156,17 +8156,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>605885</t>
+          <t>436445</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>605885</t>
+          <t>436445</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>605885</t>
+          <t>436445</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8191,17 +8191,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>974050</t>
+          <t>843524</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>974050</t>
+          <t>843524</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>974050</t>
+          <t>843524</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>187103</t>
+          <t>207690</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173156</t>
+          <t>193174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>199018</t>
+          <t>221337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8273,32 +8273,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>188750</t>
+          <t>206529</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176154</t>
+          <t>191222</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>204181</t>
+          <t>222898</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8308,32 +8308,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>375852</t>
+          <t>414219</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355800</t>
+          <t>392846</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>394592</t>
+          <t>436572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -8351,32 +8351,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24754</t>
+          <t>26493</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>45196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8386,32 +8386,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>76620</t>
+          <t>83278</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65186</t>
+          <t>71208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88280</t>
+          <t>95925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8421,32 +8421,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>108624</t>
+          <t>117854</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94457</t>
+          <t>103477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124329</t>
+          <t>133395</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -8464,32 +8464,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>44991</t>
+          <t>47293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>37955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56169</t>
+          <t>58554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>102896</t>
+          <t>112913</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90975</t>
+          <t>99747</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115378</t>
+          <t>126259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8534,32 +8534,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>147887</t>
+          <t>160206</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133689</t>
+          <t>141594</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166011</t>
+          <t>177038</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -8577,27 +8577,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>23894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47845</t>
+          <t>51677</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58623</t>
+          <t>63275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8647,32 +8647,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>62748</t>
+          <t>68111</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>57469</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74943</t>
+          <t>82609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -8690,32 +8690,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8760,32 +8760,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11273</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -8803,17 +8803,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>280155</t>
+          <t>307153</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>280155</t>
+          <t>307153</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>280155</t>
+          <t>307153</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>421925</t>
+          <t>460690</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>421925</t>
+          <t>460690</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>421925</t>
+          <t>460690</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8873,17 +8873,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>702079</t>
+          <t>767843</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>702079</t>
+          <t>767843</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>702079</t>
+          <t>767843</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8920,32 +8920,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>507695</t>
+          <t>562969</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>489981</t>
+          <t>545975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>524257</t>
+          <t>580634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8955,32 +8955,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>721887</t>
+          <t>562001</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>638243</t>
+          <t>538330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>867480</t>
+          <t>584002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8990,32 +8990,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1229582</t>
+          <t>1124971</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1155685</t>
+          <t>1092146</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1391367</t>
+          <t>1152956</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -9033,32 +9033,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>55515</t>
+          <t>60899</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>50180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69212</t>
+          <t>74025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9068,32 +9068,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>117873</t>
+          <t>128551</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59944</t>
+          <t>113616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153666</t>
+          <t>144840</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9103,32 +9103,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>173388</t>
+          <t>189450</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111567</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207125</t>
+          <t>209250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -9146,32 +9146,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>65003</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>56311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77577</t>
+          <t>82486</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>127140</t>
+          <t>140848</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67004</t>
+          <t>124490</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>165246</t>
+          <t>156488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9216,32 +9216,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>192143</t>
+          <t>209469</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>124199</t>
+          <t>189614</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228459</t>
+          <t>232060</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -9259,32 +9259,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>14009</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>28644</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>58986</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>48439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72920</t>
+          <t>71615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9329,32 +9329,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>73607</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>91116</t>
+          <t>93303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -9372,22 +9372,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>340</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>12704</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -9485,17 +9485,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9520,17 +9520,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9555,17 +9555,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
